--- a/output/pdf_financials_xlsx/STS.xlsx
+++ b/output/pdf_financials_xlsx/STS.xlsx
@@ -1296,13 +1296,13 @@
         <v>-1.031533</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.551306</v>
+        <v>-0.551306</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.075243</v>
+        <v>-0.075243</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.109877</v>
+        <v>-0.109877</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.002148</v>
@@ -1596,13 +1596,13 @@
         <v>-1.031533</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.551306</v>
+        <v>-0.551306</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.075243</v>
+        <v>-0.075243</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.109877</v>
+        <v>-0.109877</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.002148</v>
@@ -1770,13 +1770,13 @@
         <v>-1.031533</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.551306</v>
+        <v>-0.551306</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.075243</v>
+        <v>-0.075243</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.109877</v>
+        <v>-0.109877</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.002148</v>
@@ -1944,13 +1944,13 @@
         <v>14.736186</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>1.670624</v>
+        <v>-1.670624</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>2.5081</v>
+        <v>-2.5081</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>2.746925</v>
+        <v>-2.746925</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2004,13 +2004,13 @@
         <v>-1.031533</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.551306</v>
+        <v>-0.551306</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.075243</v>
+        <v>-0.075243</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.109877</v>
+        <v>-0.109877</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.002148</v>
@@ -2120,13 +2120,13 @@
         <v>-1.031533</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.551306</v>
+        <v>-0.551306</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.075243</v>
+        <v>-0.075243</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.109877</v>
+        <v>-0.109877</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.002148</v>
@@ -2270,13 +2270,13 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-0</v>
@@ -6004,31 +6004,31 @@
         <v>0</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.882142</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.273761</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.187793</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.232749</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.460219</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>4.845609</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>3.761362</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>3.874597</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>4.500792</v>
       </c>
     </row>
     <row r="93">
@@ -7497,10 +7497,10 @@
         <v>0</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>0.000929</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>0.00222</v>
       </c>
       <c r="N118" s="3" t="n">
         <v>0</v>
@@ -10382,7 +10382,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>-</t>
@@ -12824,7 +12828,11 @@
           <t>Reserves 3,874,597</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -14131,7 +14139,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -15549,7 +15561,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -16365,7 +16381,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -39244,7 +39264,11 @@
           <t>Depreciation included in exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -62163,13 +62187,13 @@
         </is>
       </c>
       <c r="K534" s="5" t="n">
-        <v>0.075243</v>
+        <v>-0.075243</v>
       </c>
       <c r="L534" s="5" t="n">
-        <v>0.109877</v>
+        <v>-0.109877</v>
       </c>
       <c r="M534" s="5" t="n">
-        <v>0.002148</v>
+        <v>-0.002148</v>
       </c>
       <c r="N534" t="inlineStr">
         <is>
@@ -64940,10 +64964,10 @@
         </is>
       </c>
       <c r="J562" s="5" t="n">
-        <v>0.551306</v>
+        <v>-0.551306</v>
       </c>
       <c r="K562" s="5" t="n">
-        <v>0.075243</v>
+        <v>-0.075243</v>
       </c>
       <c r="L562" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/STS.xlsx
+++ b/output/pdf_financials_xlsx/STS.xlsx
@@ -1049,13 +1049,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.103852</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.09518699999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.039193</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.003984</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -1088,16 +1088,16 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.131743</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.495456</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.15334</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.02206</v>
       </c>
     </row>
     <row r="13">
@@ -1989,13 +1989,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.290739</v>
+        <v>-0.394591</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.482146</v>
+        <v>-1.577333</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.443246</v>
+        <v>-1.482439</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.811034</v>
@@ -2019,7 +2019,7 @@
         <v>-0.695874</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.499741</v>
+        <v>-2.503725</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.933457</v>
@@ -2028,16 +2028,16 @@
         <v>-2.223185</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.902486</v>
+        <v>-5.034229</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-3.717378</v>
+        <v>-4.212834</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-5.604783</v>
+        <v>-5.758123</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-1.382658</v>
+        <v>-1.404718</v>
       </c>
     </row>
     <row r="28">
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.290739</v>
+        <v>-0.394591</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.482146</v>
+        <v>-1.577333</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.443246</v>
+        <v>-1.482439</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.811034</v>
@@ -2135,7 +2135,7 @@
         <v>-0.695874</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.499741</v>
+        <v>-2.503725</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.933457</v>
@@ -2144,16 +2144,16 @@
         <v>-2.221883</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.887787</v>
+        <v>-5.01953</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-3.686203</v>
+        <v>-4.181659</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-5.58409</v>
+        <v>-5.73743</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-1.367534</v>
+        <v>-1.389594</v>
       </c>
     </row>
     <row r="30">
@@ -2412,40 +2412,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.284234</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.784759</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.784759</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.291332</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.003713</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.003577</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.002502</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.004152</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.165015</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.275577</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.110795</v>
       </c>
       <c r="N34" s="3" t="n">
         <v>3.476021</v>
@@ -2528,40 +2528,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.860782</v>
+        <v>1.145016</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>2.78229</v>
+        <v>3.567049</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>2.78229</v>
+        <v>3.567049</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.750212</v>
+        <v>1.041544</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.003713</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.003577</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.002502</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.004152</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.165015</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.275577</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.110795</v>
       </c>
       <c r="N36" s="3" t="n">
         <v>3.476021</v>
@@ -3224,40 +3224,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.907851</v>
+        <v>0.623617</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.40089</v>
+        <v>0.616131</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.40089</v>
+        <v>0.616131</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.492561</v>
+        <v>0.201229</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.003713</v>
+        <v>0</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.003577</v>
+        <v>0</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.003752</v>
+        <v>0.00125</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.005402</v>
+        <v>0.00125</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.172681</v>
+        <v>0.007666</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.48855</v>
+        <v>0.212973</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.130987</v>
+        <v>0.020192</v>
       </c>
       <c r="N48" s="3" t="n">
         <v>0.151472</v>
@@ -7860,13 +7860,13 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.009467</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.015628</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.007413</v>
       </c>
       <c r="R124" s="3" t="n">
         <v>0</v>
@@ -7918,13 +7918,13 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.009467</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.015628</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.007413</v>
       </c>
       <c r="R125" s="3" t="n">
         <v>0</v>
@@ -15060,7 +15060,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
@@ -16692,7 +16692,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -17583,7 +17583,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -18997,7 +18997,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -25299,7 +25299,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -30986,7 +30990,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -52427,7 +52435,7 @@
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -55405,7 +55413,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -60292,7 +60300,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -66945,7 +66953,7 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E582" s="5" t="n">

--- a/output/pdf_financials_xlsx/STS.xlsx
+++ b/output/pdf_financials_xlsx/STS.xlsx
@@ -7097,7 +7097,7 @@
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004463</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>-0.24192</v>
@@ -8473,7 +8473,7 @@
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004463</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>-0.24192</v>
@@ -8537,7 +8537,7 @@
         <v>-1.551514</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-2.332321</v>
+        <v>-2.336784</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>9.411211</v>
@@ -36438,7 +36438,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E277" t="inlineStr">
         <is>
           <t>-</t>
@@ -43692,7 +43696,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr"/>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E349" t="inlineStr">
         <is>
           <t>-</t>
@@ -45577,7 +45585,11 @@
           <t>Shares issued for cash (net)</t>
         </is>
       </c>
-      <c r="D368" t="inlineStr"/>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E368" t="inlineStr">
         <is>
           <t>-</t>
